--- a/product_selector_out/STM32G4x3.xlsx
+++ b/product_selector_out/STM32G4x3.xlsx
@@ -17396,7 +17396,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -17462,7 +17462,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -17528,7 +17528,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -17594,7 +17594,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -17660,7 +17660,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -17726,7 +17726,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -17792,7 +17792,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -17858,7 +17858,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -17924,7 +17924,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -17990,7 +17990,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -18056,7 +18056,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -18122,7 +18122,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -18188,7 +18188,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -18254,7 +18254,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -18320,7 +18320,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -18386,7 +18386,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -18452,7 +18452,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -18518,7 +18518,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -18584,7 +18584,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -18650,7 +18650,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -18716,7 +18716,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -18782,7 +18782,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -18848,7 +18848,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -18914,7 +18914,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32G4x3.xlsx
+++ b/product_selector_out/STM32G4x3.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM35"/>
+  <dimension ref="A1:BN35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.984375" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -895,6 +896,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -990,6 +996,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1314,6 +1321,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g483ce.pdf</t>
         </is>
       </c>
@@ -1641,6 +1653,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g473cb.pdf</t>
         </is>
       </c>
@@ -1968,6 +1985,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g473cb.pdf</t>
         </is>
       </c>
@@ -2295,6 +2317,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g483ce.pdf</t>
         </is>
       </c>
@@ -2622,6 +2649,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g473cb.pdf</t>
         </is>
       </c>
@@ -2949,6 +2981,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g473cb.pdf</t>
         </is>
       </c>
@@ -3276,6 +3313,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g483ce.pdf</t>
         </is>
       </c>
@@ -3603,6 +3645,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g473cb.pdf</t>
         </is>
       </c>
@@ -3930,6 +3977,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g473cb.pdf</t>
         </is>
       </c>
@@ -4257,6 +4309,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g483ce.pdf</t>
         </is>
       </c>
@@ -4584,6 +4641,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g473cb.pdf</t>
         </is>
       </c>
@@ -4911,6 +4973,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g473cb.pdf</t>
         </is>
       </c>
@@ -5238,6 +5305,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g473cb.pdf</t>
         </is>
       </c>
@@ -5565,6 +5637,11 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g473cb.pdf</t>
         </is>
       </c>
@@ -5892,6 +5969,11 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g473cb.pdf</t>
         </is>
       </c>
@@ -6219,6 +6301,11 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g483ce.pdf</t>
         </is>
       </c>
@@ -6546,6 +6633,11 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g483ce.pdf</t>
         </is>
       </c>
@@ -6873,6 +6965,11 @@
       </c>
       <c r="BM29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g473cb.pdf</t>
         </is>
       </c>
@@ -7200,6 +7297,11 @@
       </c>
       <c r="BM30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g473cb.pdf</t>
         </is>
       </c>
@@ -7527,6 +7629,11 @@
       </c>
       <c r="BM31" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g473cb.pdf</t>
         </is>
       </c>
@@ -7854,6 +7961,11 @@
       </c>
       <c r="BM32" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g473cb.pdf</t>
         </is>
       </c>
@@ -8181,6 +8293,11 @@
       </c>
       <c r="BM33" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g473cb.pdf</t>
         </is>
       </c>
@@ -8508,6 +8625,11 @@
       </c>
       <c r="BM34" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g473cb.pdf</t>
         </is>
       </c>
@@ -8835,12 +8957,17 @@
       </c>
       <c r="BM35" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN35" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g473cb.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -8861,16 +8988,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -8883,6 +9008,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -8902,7 +9028,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -8943,7 +9071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM35"/>
+  <dimension ref="A1:BN35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9011,6 +9139,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9344,6 +9473,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -9439,6 +9573,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -9761,7 +9896,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10088,7 +10228,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10415,7 +10560,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10742,7 +10892,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11069,7 +11224,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11396,7 +11556,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11723,7 +11888,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12050,7 +12220,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12377,7 +12552,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12704,7 +12884,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13031,7 +13216,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13358,7 +13548,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13685,7 +13880,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14012,7 +14212,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
+      <c r="BM25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14339,7 +14544,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14666,7 +14876,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
+      <c r="BM27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14993,7 +15208,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
+      <c r="BM28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15320,7 +15540,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM29" s="6" t="inlineStr">
+      <c r="BM29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15647,7 +15872,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM30" s="6" t="inlineStr">
+      <c r="BM30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15974,7 +16204,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM31" s="6" t="inlineStr">
+      <c r="BM31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16301,7 +16536,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM32" s="6" t="inlineStr">
+      <c r="BM32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16628,7 +16868,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM33" s="6" t="inlineStr">
+      <c r="BM33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16955,7 +17200,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM34" s="6" t="inlineStr">
+      <c r="BM34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17282,7 +17532,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM35" s="6" t="inlineStr">
+      <c r="BM35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN35" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17290,8 +17545,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
